--- a/Logbook_pine_id_campaign.xlsx
+++ b/Logbook_pine_id_campaign.xlsx
@@ -1,136 +1,176 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26026"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\imkaaf-srv1\agm-field\Software\pine_analysis_software\files\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23AD4C07-C792-41D6-ABC6-2BBDE960A330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Tabelle1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Start time operation</t>
-  </si>
-  <si>
-    <t># operation</t>
-  </si>
-  <si>
-    <t>comments</t>
-  </si>
-  <si>
-    <t>total number of runs</t>
-  </si>
-  <si>
-    <t>Temperature (°C)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Date</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Start time operation</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t># operation</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>total number of runs</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>operation type (#)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Temperature (°C)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>Aerosol</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t>comments</t>
+    </r>
   </si>
   <si>
     <t>Aerosol</t>
   </si>
   <si>
+    <t>operation type</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>28.07.21</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>Ambient</t>
   </si>
   <si>
+    <t>background (1)</t>
+  </si>
+  <si>
     <t>ATD</t>
   </si>
   <si>
+    <t>const. Temp. (2)</t>
+  </si>
+  <si>
+    <t>SDSA01</t>
+  </si>
+  <si>
+    <t>Temp-ramp (3)</t>
+  </si>
+  <si>
+    <t>AS</t>
+  </si>
+  <si>
+    <t>Cirrus (4)</t>
+  </si>
+  <si>
     <t>ATD+AS</t>
   </si>
   <si>
-    <t>SDSA01</t>
-  </si>
-  <si>
-    <t>AS</t>
+    <t>Test (5)</t>
   </si>
   <si>
     <t>SDSA01+AS</t>
   </si>
   <si>
     <t>H2SO4</t>
-  </si>
-  <si>
-    <t>operation type</t>
-  </si>
-  <si>
-    <t>background (1)</t>
-  </si>
-  <si>
-    <t>const. Temp. (2)</t>
-  </si>
-  <si>
-    <t>Temp-ramp (3)</t>
-  </si>
-  <si>
-    <t>-22</t>
-  </si>
-  <si>
-    <t>28.07.21</t>
-  </si>
-  <si>
-    <t>11:05</t>
-  </si>
-  <si>
-    <t>operation type (#)</t>
-  </si>
-  <si>
-    <t>Cirrus (4)</t>
-  </si>
-  <si>
-    <t>Test (5)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="12"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0" tint="-0.34998626667073579"/>
-      <name val="Calibri"/>
+      <color theme="0" tint="-0.3499862666707358"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -161,28 +201,26 @@
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -190,10 +228,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -470,37 +510,37 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L459"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="11.42578125"/>
   <cols>
-    <col min="1" max="1" width="10.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19" style="3" customWidth="1"/>
-    <col min="6" max="6" width="17.85546875" style="5" customWidth="1"/>
-    <col min="7" max="7" width="48.28515625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="48.28515625" style="2" customWidth="1"/>
     <col min="8" max="8" width="56.28515625" customWidth="1"/>
     <col min="10" max="10" width="45.85546875" customWidth="1"/>
-    <col min="12" max="12" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>5</v>
@@ -508,380 +548,396 @@
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>3</v>
+      <c r="H1" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="J1" s="6"/>
       <c r="K1" s="6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="1"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
       <c r="L2" s="6"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="3">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="1">
         <v>1</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="H3" s="3"/>
+      <c r="F3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="1"/>
       <c r="J3" s="6"/>
       <c r="K3" s="6" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="L3" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G4" s="3"/>
+    <row r="4" spans="7:12" x14ac:dyDescent="0.25">
+      <c r="G4" s="1"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J5" s="6"/>
       <c r="K5" s="6" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H6" s="3"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="8:12" x14ac:dyDescent="0.25">
+      <c r="H6" s="1"/>
       <c r="J6" s="6"/>
       <c r="K6" s="6" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G7" s="3"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" x14ac:dyDescent="0.25">
+      <c r="G7" s="1"/>
       <c r="J7" s="6"/>
       <c r="K7" s="6" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J8" s="6"/>
       <c r="K8" s="6" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="L8" s="6"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H9" s="3"/>
+    <row r="9" spans="8:12" x14ac:dyDescent="0.25">
+      <c r="H9" s="1"/>
       <c r="J9" s="6"/>
       <c r="K9" s="6" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="L9" s="6"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H10" s="3"/>
+    <row r="10" spans="8:12" x14ac:dyDescent="0.25">
+      <c r="H10" s="1"/>
       <c r="J10" s="6"/>
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
+    <row r="11" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
       <c r="J13" s="6"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H14" s="3"/>
+    <row r="14" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H14" s="1"/>
       <c r="J14" s="6"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="H16" s="3"/>
+    <row r="15" spans="7:8" x14ac:dyDescent="0.25">
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+    </row>
+    <row r="16" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H16" s="1"/>
     </row>
     <row r="17" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H17" s="3"/>
+      <c r="H17" s="1"/>
     </row>
     <row r="18" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H18" s="3"/>
+      <c r="H18" s="1"/>
     </row>
     <row r="19" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H19" s="3"/>
+      <c r="H19" s="1"/>
     </row>
     <row r="20" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H20" s="3"/>
+      <c r="H20" s="1"/>
     </row>
     <row r="21" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H21" s="3"/>
+      <c r="H21" s="1"/>
     </row>
     <row r="22" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H22" s="3"/>
+      <c r="H22" s="1"/>
     </row>
     <row r="24" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H24" s="3"/>
+      <c r="H24" s="1"/>
     </row>
     <row r="27" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H27" s="3"/>
+      <c r="H27" s="1"/>
     </row>
     <row r="28" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H28" s="3"/>
+      <c r="H28" s="1"/>
     </row>
     <row r="29" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H29" s="3"/>
+      <c r="H29" s="1"/>
     </row>
     <row r="30" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H30" s="3"/>
+      <c r="H30" s="1"/>
     </row>
     <row r="31" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H31" s="3"/>
+      <c r="H31" s="1"/>
     </row>
     <row r="32" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H32" s="3"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H33" s="3"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H34" s="3"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H35" s="3"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H36" s="3"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H37" s="3"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H38" s="5"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H39" s="3"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H40" s="3"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H41" s="3"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H42" s="3"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H43" s="3"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H44" s="3"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H46" s="3"/>
+      <c r="H32" s="1"/>
+    </row>
+    <row r="33" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H33" s="1"/>
+    </row>
+    <row r="34" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H34" s="1"/>
+    </row>
+    <row r="35" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H35" s="1"/>
+    </row>
+    <row r="36" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H36" s="1"/>
+    </row>
+    <row r="37" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H37" s="1"/>
+    </row>
+    <row r="38" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H38" s="2"/>
+    </row>
+    <row r="39" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H39" s="1"/>
+    </row>
+    <row r="40" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H40" s="1"/>
+    </row>
+    <row r="41" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H41" s="1"/>
+    </row>
+    <row r="42" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H42" s="1"/>
+    </row>
+    <row r="43" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H43" s="1"/>
+    </row>
+    <row r="44" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H44" s="1"/>
+    </row>
+    <row r="46" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H46" s="1"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="9"/>
-      <c r="H47" s="3"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H48" s="3"/>
+      <c r="A47" s="7"/>
+      <c r="H47" s="1"/>
+    </row>
+    <row r="48" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H48" s="1"/>
     </row>
     <row r="49" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H49" s="3"/>
+      <c r="H49" s="1"/>
     </row>
     <row r="50" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H50" s="3"/>
+      <c r="H50" s="1"/>
     </row>
     <row r="51" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H51" s="3"/>
+      <c r="H51" s="1"/>
     </row>
     <row r="52" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H52" s="3"/>
+      <c r="H52" s="1"/>
     </row>
     <row r="53" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H53" s="3"/>
+      <c r="H53" s="1"/>
     </row>
     <row r="54" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H54" s="3"/>
+      <c r="H54" s="1"/>
     </row>
     <row r="55" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H55" s="3"/>
+      <c r="H55" s="1"/>
     </row>
     <row r="56" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H56" s="3"/>
+      <c r="H56" s="1"/>
     </row>
     <row r="57" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H57" s="3"/>
+      <c r="H57" s="1"/>
     </row>
     <row r="58" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H58" s="3"/>
+      <c r="H58" s="1"/>
     </row>
     <row r="59" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H59" s="3"/>
+      <c r="H59" s="1"/>
     </row>
     <row r="60" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H60" s="3"/>
+      <c r="H60" s="1"/>
     </row>
     <row r="61" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H61" s="3"/>
+      <c r="H61" s="1"/>
     </row>
     <row r="62" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H62" s="3"/>
+      <c r="H62" s="1"/>
     </row>
     <row r="63" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H63" s="3"/>
+      <c r="H63" s="1"/>
     </row>
     <row r="64" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H64" s="3"/>
-    </row>
-    <row r="65" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H65" s="3"/>
-    </row>
-    <row r="67" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H67" s="3"/>
-    </row>
-    <row r="68" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H68" s="3"/>
-    </row>
-    <row r="69" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H69" s="3"/>
-    </row>
-    <row r="71" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H71" s="3"/>
-    </row>
-    <row r="73" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H73" s="3"/>
-    </row>
-    <row r="75" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H75" s="3"/>
-    </row>
-    <row r="76" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H76" s="3"/>
-    </row>
-    <row r="77" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H77" s="3"/>
+      <c r="H64" s="1"/>
+    </row>
+    <row r="65" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H65" s="1"/>
+    </row>
+    <row r="67" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H67" s="1"/>
+    </row>
+    <row r="68" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H68" s="1"/>
+    </row>
+    <row r="69" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H69" s="1"/>
+    </row>
+    <row r="71" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H71" s="1"/>
+    </row>
+    <row r="73" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H73" s="1"/>
+    </row>
+    <row r="75" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H75" s="1"/>
+    </row>
+    <row r="76" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H76" s="1"/>
+    </row>
+    <row r="77" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H77" s="1"/>
     </row>
     <row r="79" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H79" s="3"/>
-      <c r="I79" s="3"/>
-    </row>
-    <row r="80" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H80" s="3"/>
-    </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="H81" s="3"/>
-    </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="H83" s="3"/>
-    </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="H86" s="3"/>
-    </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="H87" s="3"/>
-    </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="H88" s="3"/>
-    </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="E90" s="7"/>
-      <c r="H90" s="3"/>
-    </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="E91" s="7"/>
-      <c r="H91" s="3"/>
-    </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="H92" s="3"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+    </row>
+    <row r="80" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H80" s="1"/>
+    </row>
+    <row r="81" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H81" s="1"/>
+    </row>
+    <row r="83" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H83" s="1"/>
+    </row>
+    <row r="86" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H86" s="1"/>
+    </row>
+    <row r="87" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H87" s="1"/>
+    </row>
+    <row r="88" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H88" s="1"/>
+    </row>
+    <row r="90" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E90" s="8"/>
+      <c r="H90" s="1"/>
+    </row>
+    <row r="91" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E91" s="8"/>
+      <c r="H91" s="1"/>
+    </row>
+    <row r="92" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H92" s="1"/>
     </row>
     <row r="94" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B94" s="8"/>
-      <c r="H94" s="3"/>
-    </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B95" s="8"/>
+      <c r="B94" s="9"/>
+      <c r="H94" s="1"/>
+    </row>
+    <row r="95" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B95" s="9"/>
     </row>
     <row r="96" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B96" s="8"/>
-      <c r="H96" s="3"/>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B97" s="8"/>
-      <c r="H97" s="3"/>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B98" s="8"/>
-      <c r="H98" s="3"/>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B99" s="8"/>
-      <c r="H99" s="3"/>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H100" s="3"/>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B101" s="8"/>
-      <c r="H101" s="3"/>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B102" s="8"/>
-      <c r="H102" s="3"/>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B103" s="8"/>
-      <c r="H103" s="3"/>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B104" s="8"/>
-      <c r="H104" s="3"/>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B105" s="8"/>
-      <c r="H105" s="3"/>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B106" s="8"/>
-    </row>
-    <row r="107" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B96" s="9"/>
+      <c r="H96" s="1"/>
+    </row>
+    <row r="97" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B97" s="9"/>
+      <c r="H97" s="1"/>
+    </row>
+    <row r="98" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B98" s="9"/>
+      <c r="H98" s="1"/>
+    </row>
+    <row r="99" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B99" s="9"/>
+      <c r="H99" s="1"/>
+    </row>
+    <row r="100" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H100" s="1"/>
+    </row>
+    <row r="101" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B101" s="9"/>
+      <c r="H101" s="1"/>
+    </row>
+    <row r="102" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B102" s="9"/>
+      <c r="H102" s="1"/>
+    </row>
+    <row r="103" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B103" s="9"/>
+      <c r="H103" s="1"/>
+    </row>
+    <row r="104" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B104" s="9"/>
+      <c r="H104" s="1"/>
+    </row>
+    <row r="105" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B105" s="9"/>
+      <c r="H105" s="1"/>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B106" s="9"/>
+    </row>
+    <row r="107" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="11"/>
       <c r="B107" s="12"/>
       <c r="C107" s="11"/>
@@ -891,409 +947,580 @@
       <c r="G107" s="13"/>
       <c r="H107" s="11"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B108" s="8"/>
-      <c r="H108" s="3"/>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B109" s="8"/>
-      <c r="H109" s="3"/>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B110" s="8"/>
-      <c r="H110" s="3"/>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B111" s="8"/>
-      <c r="H111" s="3"/>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H112" s="3"/>
+    <row r="108" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B108" s="9"/>
+      <c r="H108" s="1"/>
+    </row>
+    <row r="109" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B109" s="9"/>
+      <c r="H109" s="1"/>
+    </row>
+    <row r="110" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B110" s="9"/>
+      <c r="H110" s="1"/>
+    </row>
+    <row r="111" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B111" s="9"/>
+      <c r="H111" s="1"/>
+    </row>
+    <row r="112" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H112" s="1"/>
     </row>
     <row r="113" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H113" s="3"/>
+      <c r="H113" s="1"/>
     </row>
     <row r="114" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H114" s="3"/>
+      <c r="H114" s="1"/>
     </row>
     <row r="115" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H115" s="3"/>
+      <c r="H115" s="1"/>
     </row>
     <row r="116" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H116" s="3"/>
+      <c r="H116" s="1"/>
     </row>
     <row r="118" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H118" s="3"/>
+      <c r="H118" s="1"/>
     </row>
     <row r="119" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H119" s="3"/>
+      <c r="H119" s="1"/>
     </row>
     <row r="120" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H120" s="3"/>
+      <c r="H120" s="1"/>
     </row>
     <row r="121" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H121" s="3"/>
+      <c r="H121" s="1"/>
     </row>
     <row r="122" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H122" s="3"/>
+      <c r="H122" s="1"/>
     </row>
     <row r="123" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H123" s="3"/>
+      <c r="H123" s="1"/>
     </row>
     <row r="125" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H125" s="3"/>
+      <c r="H125" s="1"/>
     </row>
     <row r="126" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H126" s="3"/>
+      <c r="H126" s="1"/>
     </row>
     <row r="127" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H127" s="3"/>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H129" s="3"/>
+      <c r="H127" s="1"/>
+    </row>
+    <row r="129" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H129" s="1"/>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A130" s="9"/>
-      <c r="H130" s="3"/>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H132" s="3"/>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H133" s="3"/>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A134" s="9"/>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H135" s="3"/>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H136" s="3"/>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H137" s="3"/>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H139" s="3"/>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H140" s="3"/>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H141" s="3"/>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H142" s="3"/>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H143" s="3"/>
+      <c r="A130" s="7"/>
+      <c r="H130" s="1"/>
+    </row>
+    <row r="132" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H132" s="1"/>
+    </row>
+    <row r="133" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H133" s="1"/>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" s="7"/>
+    </row>
+    <row r="135" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H135" s="1"/>
+    </row>
+    <row r="136" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H136" s="1"/>
+    </row>
+    <row r="137" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H137" s="1"/>
+    </row>
+    <row r="139" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H139" s="1"/>
+    </row>
+    <row r="140" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H140" s="1"/>
+    </row>
+    <row r="141" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H141" s="1"/>
+    </row>
+    <row r="142" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H142" s="1"/>
+    </row>
+    <row r="143" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H143" s="1"/>
     </row>
     <row r="145" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H145" s="3"/>
+      <c r="H145" s="1"/>
     </row>
     <row r="146" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H146" s="3"/>
+      <c r="H146" s="1"/>
     </row>
     <row r="147" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H147" s="3"/>
+      <c r="H147" s="1"/>
     </row>
     <row r="148" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H148" s="3"/>
+      <c r="H148" s="1"/>
     </row>
     <row r="149" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H149" s="3"/>
+      <c r="H149" s="1"/>
     </row>
     <row r="150" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H150" s="3"/>
+      <c r="H150" s="1"/>
     </row>
     <row r="151" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H151" s="3"/>
+      <c r="H151" s="1"/>
     </row>
     <row r="154" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H154" s="3"/>
+      <c r="H154" s="1"/>
     </row>
     <row r="155" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H155" s="3"/>
+      <c r="H155" s="1"/>
     </row>
     <row r="156" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H156" s="3"/>
+      <c r="H156" s="1"/>
     </row>
     <row r="158" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H158" s="3"/>
+      <c r="H158" s="1"/>
     </row>
     <row r="159" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H159" s="3"/>
+      <c r="H159" s="1"/>
     </row>
     <row r="160" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H160" s="3"/>
+      <c r="H160" s="1"/>
     </row>
     <row r="161" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H161" s="3"/>
+      <c r="H161" s="1"/>
     </row>
     <row r="162" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H162" s="3"/>
+      <c r="H162" s="1"/>
     </row>
     <row r="164" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H164" s="3"/>
+      <c r="H164" s="1"/>
     </row>
     <row r="166" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H166" s="3"/>
+      <c r="H166" s="1"/>
     </row>
     <row r="168" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H168" s="3"/>
+      <c r="H168" s="1"/>
     </row>
     <row r="170" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H170" s="3"/>
+      <c r="H170" s="1"/>
     </row>
     <row r="171" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H171" s="5"/>
+      <c r="H171" s="2"/>
     </row>
     <row r="172" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H172" s="3"/>
+      <c r="H172" s="1"/>
     </row>
     <row r="174" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H174" s="3"/>
+      <c r="H174" s="1"/>
     </row>
     <row r="175" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H175" s="5"/>
+      <c r="H175" s="2"/>
     </row>
     <row r="176" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H176" s="3"/>
+      <c r="H176" s="1"/>
     </row>
     <row r="177" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H177" s="3"/>
+      <c r="H177" s="1"/>
     </row>
     <row r="178" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H178" s="3"/>
+      <c r="H178" s="1"/>
     </row>
     <row r="180" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H180" s="3"/>
+      <c r="H180" s="1"/>
     </row>
     <row r="181" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H181" s="3"/>
+      <c r="H181" s="1"/>
     </row>
     <row r="182" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H182" s="3"/>
+      <c r="H182" s="1"/>
     </row>
     <row r="183" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H183" s="3"/>
+      <c r="H183" s="1"/>
     </row>
     <row r="184" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H184" s="3"/>
+      <c r="H184" s="1"/>
     </row>
     <row r="186" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H186" s="3"/>
+      <c r="H186" s="1"/>
     </row>
     <row r="193" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H193" s="3"/>
+      <c r="H193" s="1"/>
     </row>
     <row r="194" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H194" s="3"/>
+      <c r="H194" s="1"/>
     </row>
     <row r="195" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H195" s="3"/>
+      <c r="H195" s="1"/>
     </row>
     <row r="197" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H197" s="3"/>
+      <c r="H197" s="1"/>
     </row>
     <row r="198" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H198" s="3"/>
+      <c r="H198" s="1"/>
     </row>
     <row r="199" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H199" s="3"/>
+      <c r="H199" s="1"/>
     </row>
     <row r="200" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H200" s="3"/>
+      <c r="H200" s="1"/>
     </row>
     <row r="201" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H201" s="3"/>
+      <c r="H201" s="1"/>
     </row>
     <row r="202" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H202" s="3"/>
+      <c r="H202" s="1"/>
     </row>
     <row r="203" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H203" s="3"/>
+      <c r="H203" s="1"/>
     </row>
     <row r="204" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H204" s="3"/>
+      <c r="H204" s="1"/>
     </row>
     <row r="205" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H205" s="3"/>
+      <c r="H205" s="1"/>
     </row>
     <row r="206" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H206" s="3"/>
+      <c r="H206" s="1"/>
     </row>
     <row r="214" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H214" s="3"/>
+      <c r="H214" s="1"/>
     </row>
     <row r="215" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H215" s="3"/>
+      <c r="H215" s="1"/>
     </row>
     <row r="216" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H216" s="3"/>
+      <c r="H216" s="1"/>
     </row>
     <row r="217" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H217" s="3"/>
+      <c r="H217" s="1"/>
     </row>
     <row r="225" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="241" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H241" s="3"/>
+      <c r="H241" s="1"/>
     </row>
     <row r="243" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H243" s="3"/>
+      <c r="H243" s="1"/>
     </row>
     <row r="286" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H286" s="3"/>
+      <c r="H286" s="1"/>
     </row>
     <row r="304" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H304" s="3"/>
+      <c r="H304" s="1"/>
     </row>
     <row r="307" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H307" s="3"/>
+      <c r="H307" s="1"/>
     </row>
     <row r="310" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H310" s="3"/>
+      <c r="H310" s="1"/>
     </row>
     <row r="316" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H316" s="3"/>
+      <c r="H316" s="1"/>
     </row>
     <row r="318" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H318" s="3"/>
+      <c r="H318" s="1"/>
     </row>
     <row r="324" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H324" s="3"/>
+      <c r="H324" s="1"/>
     </row>
     <row r="325" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H325" s="3"/>
+      <c r="H325" s="1"/>
     </row>
     <row r="326" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H326" s="3"/>
+      <c r="H326" s="1"/>
     </row>
     <row r="328" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H328" s="3"/>
+      <c r="H328" s="1"/>
     </row>
     <row r="330" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H330" s="3"/>
+      <c r="H330" s="1"/>
     </row>
     <row r="332" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H332" s="3"/>
+      <c r="H332" s="1"/>
     </row>
     <row r="334" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H334" s="3"/>
+      <c r="H334" s="1"/>
     </row>
     <row r="340" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H340" s="3"/>
+      <c r="H340" s="1"/>
     </row>
     <row r="345" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H345" s="3"/>
+      <c r="H345" s="1"/>
     </row>
     <row r="351" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H351" s="3"/>
+      <c r="H351" s="1"/>
     </row>
     <row r="355" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H355" s="3"/>
+      <c r="H355" s="1"/>
     </row>
     <row r="356" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H356" s="3"/>
+      <c r="H356" s="1"/>
     </row>
     <row r="358" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H358" s="3"/>
+      <c r="H358" s="1"/>
     </row>
     <row r="359" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H359" s="3"/>
+      <c r="H359" s="1"/>
     </row>
     <row r="360" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H360" s="3"/>
+      <c r="H360" s="1"/>
     </row>
     <row r="361" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H361" s="3"/>
+      <c r="H361" s="1"/>
     </row>
     <row r="362" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H362" s="3"/>
+      <c r="H362" s="1"/>
     </row>
     <row r="367" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H367" s="3"/>
+      <c r="H367" s="1"/>
     </row>
     <row r="369" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H369" s="3"/>
+      <c r="H369" s="1"/>
     </row>
     <row r="372" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H372" s="3"/>
+      <c r="H372" s="1"/>
     </row>
     <row r="373" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H373" s="3"/>
+      <c r="H373" s="1"/>
     </row>
     <row r="377" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H377" s="3"/>
+      <c r="H377" s="1"/>
     </row>
     <row r="387" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H387" s="3"/>
+      <c r="H387" s="1"/>
     </row>
     <row r="390" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H390" s="3"/>
+      <c r="H390" s="1"/>
     </row>
     <row r="391" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H391" s="3"/>
+      <c r="H391" s="1"/>
     </row>
     <row r="392" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H392" s="3"/>
+      <c r="H392" s="1"/>
     </row>
     <row r="393" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H393" s="3"/>
+      <c r="H393" s="1"/>
     </row>
     <row r="394" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H394" s="3"/>
+      <c r="H394" s="1"/>
     </row>
     <row r="395" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H395" s="3"/>
+      <c r="H395" s="1"/>
     </row>
     <row r="396" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H396" s="3"/>
+      <c r="H396" s="1"/>
     </row>
     <row r="397" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H397" s="3"/>
+      <c r="H397" s="1"/>
     </row>
     <row r="398" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H398" s="3"/>
+      <c r="H398" s="1"/>
     </row>
     <row r="427" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H427" s="3"/>
+      <c r="H427" s="1"/>
     </row>
     <row r="434" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H434" s="3"/>
+      <c r="H434" s="1"/>
     </row>
     <row r="435" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H435" s="3"/>
+      <c r="H435" s="1"/>
     </row>
     <row r="448" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H448" s="3"/>
-    </row>
-    <row r="455" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H455" s="3"/>
-    </row>
-    <row r="457" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="H457" s="3"/>
-    </row>
-    <row r="458" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A458" s="10"/>
-    </row>
-    <row r="459" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A459" s="10"/>
+      <c r="H448" s="1"/>
+    </row>
+    <row r="455" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H455" s="1"/>
+    </row>
+    <row r="457" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H457" s="1"/>
+    </row>
+    <row r="458" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A458" s="14"/>
+    </row>
+    <row r="459" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A459" s="14"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="H96 G147 H110 H98 H100 H104:H105 H107:H108 H61:H94 H3 H15:H58 G4 G7 G13 G15 G94:G99 G102:G110 G113:G120 G135 G123:G132 G145 H112:H164 H166:H286 H288:H316 H318 H320:H357 H360 H362 H364:H373 H375:H390 H392:H1048576" xr:uid="{00000000-0002-0000-0000-000002000000}">
-      <formula1>$J$3:$J$10</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="F94:F111 G3 G17:G24 H38 G27:G37 G39:G44 G46:G49 G52:G55 G58:G59 G62:G65 G68:G72 G75:G78 G81:G90 G93 G136:G137 G140:G144 H171 G146:G170 H175 G172:G174 G176:G358 G360:G391 G393:G1048576" xr:uid="{00000000-0002-0000-0000-000003000000}">
-      <formula1>"Ambient,AS,ATD,SDSA01,ATD+AS,SDSA01+AS,H2SO4"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E1048576" xr:uid="{79F9FE4B-88EF-40C9-A137-5CAA5015BC2E}">
+  <dataValidations count="60">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E10:E1048576">
       <formula1>$L$3:$L$7</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E1048576">
+      <formula1>$L$3:$L$7</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="F100:F111">
+      <formula1>"Ambient,AS,ATD,SDSA01,ATD+AS,SDSA01+AS,H2SO4"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="F94:F111">
+      <formula1>"Ambient,AS,ATD,SDSA01,ATD+AS,SDSA01+AS,H2SO4"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G1000:G1048576">
+      <formula1>"Ambient,AS,ATD,SDSA01,ATD+AS,SDSA01+AS,H2SO4"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G102:G110">
+      <formula1>$J$3:$J$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G113:H120">
+      <formula1>$J$3:$J$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G123:H132">
+      <formula1>$J$3:$J$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G13">
+      <formula1>$J$3:$J$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G135:H135">
+      <formula1>$J$3:$J$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G136:G137">
+      <formula1>"Ambient,AS,ATD,SDSA01,ATD+AS,SDSA01+AS,H2SO4"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G140:G144">
+      <formula1>"Ambient,AS,ATD,SDSA01,ATD+AS,SDSA01+AS,H2SO4"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G145:H145">
+      <formula1>$J$3:$J$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G146:G170">
+      <formula1>"Ambient,AS,ATD,SDSA01,ATD+AS,SDSA01+AS,H2SO4"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G15:H15">
+      <formula1>$J$3:$J$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G17:G24">
+      <formula1>"Ambient,AS,ATD,SDSA01,ATD+AS,SDSA01+AS,H2SO4"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G172:G174">
+      <formula1>"Ambient,AS,ATD,SDSA01,ATD+AS,SDSA01+AS,H2SO4"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G176:G358">
+      <formula1>"Ambient,AS,ATD,SDSA01,ATD+AS,SDSA01+AS,H2SO4"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G27:G37">
+      <formula1>"Ambient,AS,ATD,SDSA01,ATD+AS,SDSA01+AS,H2SO4"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G3">
+      <formula1>"Ambient,AS,ATD,SDSA01,ATD+AS,SDSA01+AS,H2SO4"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G360:G391">
+      <formula1>"Ambient,AS,ATD,SDSA01,ATD+AS,SDSA01+AS,H2SO4"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G39:G44">
+      <formula1>"Ambient,AS,ATD,SDSA01,ATD+AS,SDSA01+AS,H2SO4"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G393:G1048576">
+      <formula1>"Ambient,AS,ATD,SDSA01,ATD+AS,SDSA01+AS,H2SO4"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G4">
+      <formula1>$J$3:$J$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G46:G49">
+      <formula1>"Ambient,AS,ATD,SDSA01,ATD+AS,SDSA01+AS,H2SO4"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G52:G55">
+      <formula1>"Ambient,AS,ATD,SDSA01,ATD+AS,SDSA01+AS,H2SO4"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G58:G59">
+      <formula1>"Ambient,AS,ATD,SDSA01,ATD+AS,SDSA01+AS,H2SO4"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G62:G65">
+      <formula1>"Ambient,AS,ATD,SDSA01,ATD+AS,SDSA01+AS,H2SO4"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G68:G72">
+      <formula1>"Ambient,AS,ATD,SDSA01,ATD+AS,SDSA01+AS,H2SO4"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G7">
+      <formula1>$J$3:$J$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G75:G78">
+      <formula1>"Ambient,AS,ATD,SDSA01,ATD+AS,SDSA01+AS,H2SO4"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G81:G90">
+      <formula1>"Ambient,AS,ATD,SDSA01,ATD+AS,SDSA01+AS,H2SO4"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G93">
+      <formula1>"Ambient,AS,ATD,SDSA01,ATD+AS,SDSA01+AS,H2SO4"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="G94:G99">
+      <formula1>$J$3:$J$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="H100">
+      <formula1>$J$3:$J$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="H1000:H1048576">
+      <formula1>$J$3:$J$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="H104:H105">
+      <formula1>$J$3:$J$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="H107:H108">
+      <formula1>$J$3:$J$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="H110">
+      <formula1>$J$3:$J$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="H112:H164">
+      <formula1>$J$3:$J$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="H16:H37">
+      <formula1>$J$3:$J$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="H166:H170">
+      <formula1>$J$3:$J$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="H171">
+      <formula1>"Ambient,AS,ATD,SDSA01,ATD+AS,SDSA01+AS,H2SO4"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="H172:H174">
+      <formula1>$J$3:$J$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="H175">
+      <formula1>"Ambient,AS,ATD,SDSA01,ATD+AS,SDSA01+AS,H2SO4"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="H176:H286">
+      <formula1>$J$3:$J$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="H288:H316">
+      <formula1>$J$3:$J$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="H3">
+      <formula1>$J$3:$J$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="H318">
+      <formula1>$J$3:$J$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="H320:H357">
+      <formula1>$J$3:$J$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="H360">
+      <formula1>$J$3:$J$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="H362">
+      <formula1>$J$3:$J$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="H364:H373">
+      <formula1>$J$3:$J$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="H375:H390">
+      <formula1>$J$3:$J$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="H38">
+      <formula1>"Ambient,AS,ATD,SDSA01,ATD+AS,SDSA01+AS,H2SO4"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="H39:H58">
+      <formula1>$J$3:$J$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="H392:H1048576">
+      <formula1>$J$3:$J$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="H61:H94">
+      <formula1>$J$3:$J$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="H96">
+      <formula1>$J$3:$J$10</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" sqref="H98">
+      <formula1>$J$3:$J$10</formula1>
+    </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.787401575" bottom="0.787401575" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>